--- a/data/trans_bre/P1427-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P1427-Estudios-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,89</t>
+          <t>3,09</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>30,15%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 2,9</t>
+          <t>-0,99; 2,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 5,07</t>
+          <t>1,22; 4,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 5,84</t>
+          <t>0,45; 5,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,54; 73,02</t>
+          <t>-16,19; 74,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,91; 257,4</t>
+          <t>28,89; 257,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 61,14</t>
+          <t>5,11; 70,46</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 0,39</t>
+          <t>-0,8; 0,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 0,91</t>
+          <t>-0,18; 0,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,79</t>
+          <t>-0,66; 0,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-79,37; 86,44</t>
+          <t>-75,9; 78,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-26,56; 271,2</t>
+          <t>-26,24; 260,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,66; 62,23</t>
+          <t>-29,45; 48,43</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,4</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>41,66%</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 0,91</t>
+          <t>-0,99; 0,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 1,87</t>
+          <t>-0,59; 1,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 1,95</t>
+          <t>-0,5; 1,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -814,12 +814,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-73,31; 714,66</t>
+          <t>-70,83; 829,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-38,41; 192,8</t>
+          <t>-29,21; 211,93</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,24</t>
+          <t>1,32</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>42,45%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 1,4</t>
+          <t>-0,17; 1,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,86</t>
+          <t>0,64; 1,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,18</t>
+          <t>0,58; 2,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 81,35</t>
+          <t>-8,66; 84,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>48,04; 235,13</t>
+          <t>47,0; 221,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,19; 86,64</t>
+          <t>16,44; 74,79</t>
         </is>
       </c>
     </row>
